--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:28:34+00:00</t>
+    <t>2026-04-29T09:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
+++ b/r5-ELGA-MOPED-main/CodeSystem-VAEStatusCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
